--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2020_valparaiso.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2020_valparaiso.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>24.68484505218869</v>
+      </c>
+      <c r="C2">
         <v>33.79723278582409</v>
-      </c>
-      <c r="C2">
-        <v>24.68484505218869</v>
       </c>
       <c r="D2">
         <v>2.958822121139574</v>
       </c>
       <c r="E2">
+        <v>15.57579594420732</v>
+      </c>
+      <c r="F2">
+        <v>63.09861743623256</v>
+      </c>
+      <c r="G2">
         <v>21.32558661956011</v>
-      </c>
-      <c r="F2">
-        <v>63.09861743623257</v>
-      </c>
-      <c r="G2">
-        <v>15.57579594420733</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>27.72755699584968</v>
+      </c>
+      <c r="C3">
         <v>29.36494399909034</v>
-      </c>
-      <c r="C3">
-        <v>27.72755699584968</v>
       </c>
       <c r="D3">
         <v>3.405421103581801</v>
       </c>
       <c r="E3">
-        <v>18.69277261047374</v>
+        <v>17.6504650573631</v>
       </c>
       <c r="F3">
         <v>63.65676233216315</v>
       </c>
       <c r="G3">
-        <v>17.6504650573631</v>
+        <v>18.69277261047374</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>25.76448077926596</v>
+      </c>
+      <c r="C4">
         <v>30.41920333971125</v>
-      </c>
-      <c r="C4">
-        <v>25.76448077926596</v>
       </c>
       <c r="D4">
         <v>3.287397072278134</v>
       </c>
       <c r="E4">
-        <v>19.47655640939971</v>
+        <v>16.49626907227976</v>
       </c>
       <c r="F4">
         <v>64.02717451832052</v>
       </c>
       <c r="G4">
-        <v>16.49626907227976</v>
+        <v>19.47655640939971</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>36.43564356435643</v>
+      </c>
+      <c r="C5">
         <v>29.3069306930693</v>
-      </c>
-      <c r="C5">
-        <v>36.43564356435643</v>
       </c>
       <c r="D5">
         <v>3.412162162162162</v>
       </c>
       <c r="E5">
-        <v>17.68219832735961</v>
+        <v>21.98327359617682</v>
       </c>
       <c r="F5">
         <v>60.33452807646356</v>
       </c>
       <c r="G5">
-        <v>21.98327359617682</v>
+        <v>17.68219832735961</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>32.64797507788162</v>
+      </c>
+      <c r="C6">
         <v>35.51401869158878</v>
-      </c>
-      <c r="C6">
-        <v>32.64797507788162</v>
       </c>
       <c r="D6">
         <v>2.815789473684211</v>
       </c>
       <c r="E6">
-        <v>21.11893293812523</v>
+        <v>19.41459799925898</v>
       </c>
       <c r="F6">
         <v>59.46646906261579</v>
       </c>
       <c r="G6">
-        <v>19.41459799925898</v>
+        <v>21.11893293812523</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>30.8020389056486</v>
+      </c>
+      <c r="C7">
         <v>32.46125039009674</v>
-      </c>
-      <c r="C7">
-        <v>30.8020389056486</v>
       </c>
       <c r="D7">
         <v>3.080596058323986</v>
       </c>
       <c r="E7">
-        <v>19.88276147695052</v>
+        <v>18.86648188855968</v>
       </c>
       <c r="F7">
         <v>61.25075663448979</v>
       </c>
       <c r="G7">
-        <v>18.86648188855968</v>
+        <v>19.88276147695052</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>24.18942298583516</v>
+      </c>
+      <c r="C8">
         <v>36.35742669531877</v>
-      </c>
-      <c r="C8">
-        <v>24.18942298583516</v>
       </c>
       <c r="D8">
         <v>2.750469686372924</v>
       </c>
       <c r="E8">
-        <v>22.64599197525497</v>
+        <v>15.06689357896175</v>
       </c>
       <c r="F8">
         <v>62.28711444578328</v>
       </c>
       <c r="G8">
-        <v>15.06689357896175</v>
+        <v>22.64599197525497</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>32.91092061125605</v>
+      </c>
+      <c r="C9">
         <v>15.91502049944092</v>
-      </c>
-      <c r="C9">
-        <v>32.91092061125605</v>
       </c>
       <c r="D9">
         <v>6.283372365339578</v>
       </c>
       <c r="E9">
-        <v>10.69371399949912</v>
+        <v>22.11369897320311</v>
       </c>
       <c r="F9">
-        <v>67.19258702729776</v>
+        <v>67.19258702729778</v>
       </c>
       <c r="G9">
-        <v>22.1136989732031</v>
+        <v>10.69371399949913</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>26.93123295970918</v>
+      </c>
+      <c r="C10">
         <v>30.73194603034046</v>
-      </c>
-      <c r="C10">
-        <v>26.93123295970918</v>
       </c>
       <c r="D10">
         <v>3.253942978465271</v>
       </c>
       <c r="E10">
-        <v>19.49215170415915</v>
+        <v>17.08149812291229</v>
       </c>
       <c r="F10">
         <v>63.42635017292856</v>
       </c>
       <c r="G10">
-        <v>17.08149812291229</v>
+        <v>19.49215170415915</v>
       </c>
     </row>
     <row r="11">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="B11">
+        <v>31.63062780737491</v>
+      </c>
+      <c r="C11">
         <v>25.61370521257704</v>
-      </c>
-      <c r="C11">
-        <v>31.63062780737491</v>
       </c>
       <c r="D11">
         <v>3.90415986949429</v>
       </c>
       <c r="E11">
-        <v>16.28911180495582</v>
+        <v>20.11559157642995</v>
       </c>
       <c r="F11">
         <v>63.59529661861423</v>
       </c>
       <c r="G11">
-        <v>20.11559157642995</v>
+        <v>16.28911180495582</v>
       </c>
     </row>
     <row r="12">
@@ -648,22 +648,22 @@
         </is>
       </c>
       <c r="B12">
+        <v>28.98343803540834</v>
+      </c>
+      <c r="C12">
         <v>27.22729868646488</v>
-      </c>
-      <c r="C12">
-        <v>28.98343803540834</v>
       </c>
       <c r="D12">
         <v>3.67278447823807</v>
       </c>
       <c r="E12">
-        <v>17.42985101910246</v>
+        <v>18.55406269993602</v>
       </c>
       <c r="F12">
         <v>64.01608628096152</v>
       </c>
       <c r="G12">
-        <v>18.55406269993602</v>
+        <v>17.42985101910246</v>
       </c>
     </row>
     <row r="13">
@@ -673,22 +673,22 @@
         </is>
       </c>
       <c r="B13">
+        <v>28.81495511817508</v>
+      </c>
+      <c r="C13">
         <v>28.93024787943671</v>
-      </c>
-      <c r="C13">
-        <v>28.81495511817508</v>
       </c>
       <c r="D13">
         <v>3.456589809279818</v>
       </c>
       <c r="E13">
-        <v>18.33985904463587</v>
+        <v>18.2667710780475</v>
       </c>
       <c r="F13">
         <v>63.39336987731663</v>
       </c>
       <c r="G13">
-        <v>18.2667710780475</v>
+        <v>18.33985904463587</v>
       </c>
     </row>
     <row r="14">
@@ -698,22 +698,22 @@
         </is>
       </c>
       <c r="B14">
+        <v>26.71230017947327</v>
+      </c>
+      <c r="C14">
         <v>31.9838056680162</v>
-      </c>
-      <c r="C14">
-        <v>26.71230017947327</v>
       </c>
       <c r="D14">
         <v>3.126582278481012</v>
       </c>
       <c r="E14">
-        <v>20.15412129819578</v>
+        <v>16.83236021250855</v>
       </c>
       <c r="F14">
         <v>63.01351848929567</v>
       </c>
       <c r="G14">
-        <v>16.83236021250855</v>
+        <v>20.15412129819578</v>
       </c>
     </row>
     <row r="15">
@@ -723,22 +723,22 @@
         </is>
       </c>
       <c r="B15">
+        <v>27.44262540180907</v>
+      </c>
+      <c r="C15">
         <v>30.08895866038723</v>
-      </c>
-      <c r="C15">
-        <v>27.44262540180907</v>
       </c>
       <c r="D15">
         <v>3.323478260869565</v>
       </c>
       <c r="E15">
+        <v>17.42039576709533</v>
+      </c>
+      <c r="F15">
+        <v>63.47933374460209</v>
+      </c>
+      <c r="G15">
         <v>19.10027048830257</v>
-      </c>
-      <c r="F15">
-        <v>63.47933374460211</v>
-      </c>
-      <c r="G15">
-        <v>17.42039576709534</v>
       </c>
     </row>
     <row r="16">
@@ -748,22 +748,22 @@
         </is>
       </c>
       <c r="B16">
+        <v>26.24869927159209</v>
+      </c>
+      <c r="C16">
         <v>34.41727367325703</v>
-      </c>
-      <c r="C16">
-        <v>26.24869927159209</v>
       </c>
       <c r="D16">
         <v>2.90551776266062</v>
       </c>
       <c r="E16">
-        <v>21.42163212435233</v>
+        <v>16.33743523316062</v>
       </c>
       <c r="F16">
-        <v>62.24093264248704</v>
+        <v>62.24093264248705</v>
       </c>
       <c r="G16">
-        <v>16.33743523316062</v>
+        <v>21.42163212435234</v>
       </c>
     </row>
     <row r="17">
@@ -773,22 +773,22 @@
         </is>
       </c>
       <c r="B17">
+        <v>27.09570957095709</v>
+      </c>
+      <c r="C17">
         <v>34.85148514851485</v>
-      </c>
-      <c r="C17">
-        <v>27.09570957095709</v>
       </c>
       <c r="D17">
         <v>2.869318181818182</v>
       </c>
       <c r="E17">
-        <v>21.52027715508457</v>
+        <v>16.7312003260648</v>
       </c>
       <c r="F17">
         <v>61.74852251885062</v>
       </c>
       <c r="G17">
-        <v>16.7312003260648</v>
+        <v>21.52027715508457</v>
       </c>
     </row>
     <row r="18">
@@ -798,22 +798,22 @@
         </is>
       </c>
       <c r="B18">
+        <v>25.97454256165473</v>
+      </c>
+      <c r="C18">
         <v>34.54653937947494</v>
-      </c>
-      <c r="C18">
-        <v>25.97454256165473</v>
       </c>
       <c r="D18">
         <v>2.894645941278066</v>
       </c>
       <c r="E18">
+        <v>16.1813901623095</v>
+      </c>
+      <c r="F18">
+        <v>62.29711312105068</v>
+      </c>
+      <c r="G18">
         <v>21.52149671663982</v>
-      </c>
-      <c r="F18">
-        <v>62.29711312105066</v>
-      </c>
-      <c r="G18">
-        <v>16.1813901623095</v>
       </c>
     </row>
     <row r="19">
@@ -823,22 +823,22 @@
         </is>
       </c>
       <c r="B19">
+        <v>25.68864809955134</v>
+      </c>
+      <c r="C19">
         <v>31.97324980953187</v>
-      </c>
-      <c r="C19">
-        <v>25.68864809955134</v>
       </c>
       <c r="D19">
         <v>3.127614508869473</v>
       </c>
       <c r="E19">
-        <v>20.27963016655391</v>
+        <v>16.29350429002502</v>
       </c>
       <c r="F19">
         <v>63.42686554342107</v>
       </c>
       <c r="G19">
-        <v>16.29350429002502</v>
+        <v>20.27963016655391</v>
       </c>
     </row>
     <row r="20">
@@ -848,22 +848,22 @@
         </is>
       </c>
       <c r="B20">
+        <v>28.38654798432421</v>
+      </c>
+      <c r="C20">
         <v>32.34498891150469</v>
-      </c>
-      <c r="C20">
-        <v>28.38654798432421</v>
       </c>
       <c r="D20">
         <v>3.091669014745938</v>
       </c>
       <c r="E20">
-        <v>20.12361079609889</v>
+        <v>17.66084524079535</v>
       </c>
       <c r="F20">
         <v>62.21554396310577</v>
       </c>
       <c r="G20">
-        <v>17.66084524079535</v>
+        <v>20.12361079609889</v>
       </c>
     </row>
     <row r="21">
@@ -873,22 +873,22 @@
         </is>
       </c>
       <c r="B21">
+        <v>22.98941798941799</v>
+      </c>
+      <c r="C21">
         <v>25.02645502645503</v>
-      </c>
-      <c r="C21">
-        <v>22.98941798941799</v>
       </c>
       <c r="D21">
         <v>3.995771670190275</v>
       </c>
       <c r="E21">
-        <v>16.90795352993744</v>
+        <v>15.53172475424486</v>
       </c>
       <c r="F21">
         <v>67.56032171581769</v>
       </c>
       <c r="G21">
-        <v>15.53172475424486</v>
+        <v>16.90795352993744</v>
       </c>
     </row>
     <row r="22">
@@ -898,22 +898,22 @@
         </is>
       </c>
       <c r="B22">
+        <v>30.27986438875224</v>
+      </c>
+      <c r="C22">
         <v>27.70723924749053</v>
-      </c>
-      <c r="C22">
-        <v>30.27986438875224</v>
       </c>
       <c r="D22">
         <v>3.609165067178503</v>
       </c>
       <c r="E22">
-        <v>17.53765884036018</v>
+        <v>19.16603551291761</v>
       </c>
       <c r="F22">
         <v>63.29630564672222</v>
       </c>
       <c r="G22">
-        <v>19.16603551291761</v>
+        <v>17.53765884036018</v>
       </c>
     </row>
     <row r="23">
@@ -923,22 +923,22 @@
         </is>
       </c>
       <c r="B23">
+        <v>27.239092495637</v>
+      </c>
+      <c r="C23">
         <v>34.69458987783595</v>
-      </c>
-      <c r="C23">
-        <v>27.239092495637</v>
       </c>
       <c r="D23">
         <v>2.882293762575453</v>
       </c>
       <c r="E23">
-        <v>21.42518429107212</v>
+        <v>16.82114066474113</v>
       </c>
       <c r="F23">
         <v>61.75367504418675</v>
       </c>
       <c r="G23">
-        <v>16.82114066474113</v>
+        <v>21.42518429107212</v>
       </c>
     </row>
     <row r="24">
@@ -948,22 +948,22 @@
         </is>
       </c>
       <c r="B24">
+        <v>26.80519480519481</v>
+      </c>
+      <c r="C24">
         <v>31.48722245496439</v>
-      </c>
-      <c r="C24">
-        <v>26.80519480519481</v>
       </c>
       <c r="D24">
         <v>3.17589143161256</v>
       </c>
       <c r="E24">
-        <v>19.89180720085538</v>
+        <v>16.933972750659</v>
       </c>
       <c r="F24">
         <v>63.17422004848562</v>
       </c>
       <c r="G24">
-        <v>16.933972750659</v>
+        <v>19.89180720085538</v>
       </c>
     </row>
     <row r="25">
@@ -973,22 +973,22 @@
         </is>
       </c>
       <c r="B25">
+        <v>27.95099004485286</v>
+      </c>
+      <c r="C25">
         <v>47.53309265944645</v>
-      </c>
-      <c r="C25">
-        <v>27.95099004485286</v>
       </c>
       <c r="D25">
         <v>2.10379746835443</v>
       </c>
       <c r="E25">
-        <v>27.08683997257029</v>
+        <v>15.92793466741475</v>
       </c>
       <c r="F25">
         <v>56.98522536001496</v>
       </c>
       <c r="G25">
-        <v>15.92793466741475</v>
+        <v>27.08683997257029</v>
       </c>
     </row>
     <row r="26">
@@ -998,22 +998,22 @@
         </is>
       </c>
       <c r="B26">
+        <v>30.83453138906004</v>
+      </c>
+      <c r="C26">
         <v>39.97398507564866</v>
-      </c>
-      <c r="C26">
-        <v>30.83453138906004</v>
       </c>
       <c r="D26">
         <v>2.501626990923103</v>
       </c>
       <c r="E26">
-        <v>23.40280561122244</v>
+        <v>18.05210420841683</v>
       </c>
       <c r="F26">
         <v>58.54509018036072</v>
       </c>
       <c r="G26">
-        <v>18.05210420841683</v>
+        <v>23.40280561122244</v>
       </c>
     </row>
     <row r="27">
@@ -1023,22 +1023,22 @@
         </is>
       </c>
       <c r="B27">
+        <v>29.10617283950617</v>
+      </c>
+      <c r="C27">
         <v>47.78271604938272</v>
-      </c>
-      <c r="C27">
-        <v>29.10617283950617</v>
       </c>
       <c r="D27">
         <v>2.092806945018603</v>
       </c>
       <c r="E27">
-        <v>27.01284198771636</v>
+        <v>16.45449469570072</v>
       </c>
       <c r="F27">
         <v>56.53266331658291</v>
       </c>
       <c r="G27">
-        <v>16.45449469570072</v>
+        <v>27.01284198771636</v>
       </c>
     </row>
     <row r="28">
@@ -1048,22 +1048,22 @@
         </is>
       </c>
       <c r="B28">
+        <v>28.95253493474997</v>
+      </c>
+      <c r="C28">
         <v>51.17219078415521</v>
-      </c>
-      <c r="C28">
-        <v>28.95253493474997</v>
       </c>
       <c r="D28">
         <v>1.954186413902054</v>
       </c>
       <c r="E28">
-        <v>28.4093094825928</v>
+        <v>16.07360389818555</v>
       </c>
       <c r="F28">
         <v>55.51708661922164</v>
       </c>
       <c r="G28">
-        <v>16.07360389818555</v>
+        <v>28.4093094825928</v>
       </c>
     </row>
     <row r="29">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="B29">
+        <v>26.74559397282389</v>
+      </c>
+      <c r="C29">
         <v>33.7010628279295</v>
-      </c>
-      <c r="C29">
-        <v>26.74559397282389</v>
       </c>
       <c r="D29">
         <v>2.967265469061876</v>
       </c>
       <c r="E29">
+        <v>16.66946168036223</v>
+      </c>
+      <c r="F29">
+        <v>62.32601039745094</v>
+      </c>
+      <c r="G29">
         <v>21.00452792218682</v>
-      </c>
-      <c r="F29">
-        <v>62.32601039745096</v>
-      </c>
-      <c r="G29">
-        <v>16.66946168036224</v>
       </c>
     </row>
     <row r="30">
@@ -1098,22 +1098,22 @@
         </is>
       </c>
       <c r="B30">
+        <v>27.53363570530167</v>
+      </c>
+      <c r="C30">
         <v>27.5641269962267</v>
-      </c>
-      <c r="C30">
-        <v>27.53363570530167</v>
       </c>
       <c r="D30">
         <v>3.627903761061947</v>
       </c>
       <c r="E30">
-        <v>17.7720983953014</v>
+        <v>17.75243899442165</v>
       </c>
       <c r="F30">
         <v>64.47546261027695</v>
       </c>
       <c r="G30">
-        <v>17.75243899442165</v>
+        <v>17.7720983953014</v>
       </c>
     </row>
     <row r="31">
@@ -1123,22 +1123,22 @@
         </is>
       </c>
       <c r="B31">
+        <v>28.40605520926091</v>
+      </c>
+      <c r="C31">
         <v>31.78984861976848</v>
-      </c>
-      <c r="C31">
-        <v>28.40605520926091</v>
       </c>
       <c r="D31">
         <v>3.145658263305322</v>
       </c>
       <c r="E31">
-        <v>19.8443579766537</v>
+        <v>17.73207337409672</v>
       </c>
       <c r="F31">
         <v>62.4235686492496</v>
       </c>
       <c r="G31">
-        <v>17.73207337409672</v>
+        <v>19.8443579766537</v>
       </c>
     </row>
     <row r="32">
@@ -1148,22 +1148,22 @@
         </is>
       </c>
       <c r="B32">
+        <v>30.34795013334987</v>
+      </c>
+      <c r="C32">
         <v>30.19909446132854</v>
-      </c>
-      <c r="C32">
-        <v>30.34795013334987</v>
       </c>
       <c r="D32">
         <v>3.311357568289176</v>
       </c>
       <c r="E32">
-        <v>18.81012169209967</v>
+        <v>18.90283948232567</v>
       </c>
       <c r="F32">
         <v>62.28703882557465</v>
       </c>
       <c r="G32">
-        <v>18.90283948232567</v>
+        <v>18.81012169209967</v>
       </c>
     </row>
     <row r="33">
@@ -1173,22 +1173,22 @@
         </is>
       </c>
       <c r="B33">
+        <v>24.46216617210683</v>
+      </c>
+      <c r="C33">
         <v>27.96735905044511</v>
-      </c>
-      <c r="C33">
-        <v>24.46216617210683</v>
       </c>
       <c r="D33">
         <v>3.575596816976127</v>
       </c>
       <c r="E33">
-        <v>18.34773086750213</v>
+        <v>16.04818104392262</v>
       </c>
       <c r="F33">
         <v>65.60408808857524</v>
       </c>
       <c r="G33">
-        <v>16.04818104392262</v>
+        <v>18.34773086750213</v>
       </c>
     </row>
     <row r="34">
@@ -1198,22 +1198,22 @@
         </is>
       </c>
       <c r="B34">
+        <v>28.39460214053048</v>
+      </c>
+      <c r="C34">
         <v>34.48115402512797</v>
-      </c>
-      <c r="C34">
-        <v>28.39460214053048</v>
       </c>
       <c r="D34">
         <v>2.900134952766532</v>
       </c>
       <c r="E34">
-        <v>21.17021884463745</v>
+        <v>17.43328952631278</v>
       </c>
       <c r="F34">
         <v>61.39649162904976</v>
       </c>
       <c r="G34">
-        <v>17.43328952631278</v>
+        <v>21.17021884463745</v>
       </c>
     </row>
     <row r="35">
@@ -1223,22 +1223,22 @@
         </is>
       </c>
       <c r="B35">
+        <v>29.29465910307182</v>
+      </c>
+      <c r="C35">
         <v>30.21513432516322</v>
-      </c>
-      <c r="C35">
-        <v>29.29465910307182</v>
       </c>
       <c r="D35">
         <v>3.309599716613532</v>
       </c>
       <c r="E35">
-        <v>18.94249479970476</v>
+        <v>18.36542977923908</v>
       </c>
       <c r="F35">
         <v>62.69207542105616</v>
       </c>
       <c r="G35">
-        <v>18.36542977923908</v>
+        <v>18.94249479970476</v>
       </c>
     </row>
     <row r="36">
@@ -1248,22 +1248,22 @@
         </is>
       </c>
       <c r="B36">
+        <v>23.65843918764737</v>
+      </c>
+      <c r="C36">
         <v>34.215980832129</v>
-      </c>
-      <c r="C36">
-        <v>23.65843918764737</v>
       </c>
       <c r="D36">
         <v>2.92261094284047</v>
       </c>
       <c r="E36">
-        <v>21.67290991652915</v>
+        <v>14.985606398227</v>
       </c>
       <c r="F36">
         <v>63.34148368524384</v>
       </c>
       <c r="G36">
-        <v>14.985606398227</v>
+        <v>21.67290991652915</v>
       </c>
     </row>
     <row r="37">
@@ -1273,22 +1273,22 @@
         </is>
       </c>
       <c r="B37">
+        <v>24.55624745387884</v>
+      </c>
+      <c r="C37">
         <v>30.6669382529244</v>
-      </c>
-      <c r="C37">
-        <v>24.55624745387884</v>
       </c>
       <c r="D37">
         <v>3.260840686972199</v>
       </c>
       <c r="E37">
-        <v>19.75667366526694</v>
+        <v>15.81996100779844</v>
       </c>
       <c r="F37">
         <v>64.42336532693461</v>
       </c>
       <c r="G37">
-        <v>15.81996100779844</v>
+        <v>19.75667366526694</v>
       </c>
     </row>
     <row r="38">
@@ -1298,22 +1298,22 @@
         </is>
       </c>
       <c r="B38">
+        <v>26.96549898526428</v>
+      </c>
+      <c r="C38">
         <v>37.84523074208065</v>
-      </c>
-      <c r="C38">
-        <v>26.96549898526428</v>
       </c>
       <c r="D38">
         <v>2.642340871998135</v>
       </c>
       <c r="E38">
-        <v>22.96284398757897</v>
+        <v>16.36149480672449</v>
       </c>
       <c r="F38">
         <v>60.67566120569654</v>
       </c>
       <c r="G38">
-        <v>16.36149480672449</v>
+        <v>22.96284398757897</v>
       </c>
     </row>
     <row r="39">
@@ -1323,22 +1323,22 @@
         </is>
       </c>
       <c r="B39">
+        <v>27.41937521316777</v>
+      </c>
+      <c r="C39">
         <v>32.79183456918005</v>
-      </c>
-      <c r="C39">
-        <v>27.41937521316777</v>
       </c>
       <c r="D39">
         <v>3.049539658692554</v>
       </c>
       <c r="E39">
-        <v>20.46787775570063</v>
+        <v>17.11451729901914</v>
       </c>
       <c r="F39">
         <v>62.41760494528022</v>
       </c>
       <c r="G39">
-        <v>17.11451729901914</v>
+        <v>20.46787775570063</v>
       </c>
     </row>
   </sheetData>
